--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27203"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/anuj_talwar_wri_org/Documents/EPS/Transport/Input Data/Draft US 4.0/BVS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A07E0BB-D667-4AB7-A44B-41B4CC28EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{B81DBE57-2E0B-492A-8B39-306C57ECFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E09122C-4500-40D1-9C2B-7BAB581A9537}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -260,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,7 +541,7 @@
     <cellStyle name="Parent row 2" xfId="28" xr:uid="{1C336998-EB49-46ED-B880-BDD7385C1A9F}"/>
     <cellStyle name="Parent row 3" xfId="21" xr:uid="{E39AA093-46A1-425E-9FAB-5E5D22915C9B}"/>
     <cellStyle name="Parent row 4" xfId="13" xr:uid="{766EEC84-3128-426E-8720-CF77BEFFA340}"/>
-    <cellStyle name="Percent" xfId="30" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="30" builtinId="5"/>
     <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Table title 2" xfId="29" xr:uid="{75C5CFB8-5852-4F3E-A011-ECC9372E7F45}"/>
     <cellStyle name="Table title 3" xfId="22" xr:uid="{D3D003D1-845D-4DC8-878D-F5771072DB44}"/>
@@ -848,17 +848,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -874,7 +874,7 @@
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -890,7 +890,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -898,7 +898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -906,7 +906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -914,119 +914,119 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="13">
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>54.77</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>75.807100000000005</v>
       </c>
@@ -1045,22 +1045,22 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>10000000</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>100000</v>
       </c>
@@ -1082,12 +1082,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8:M8" si="3">L2</f>
+        <f t="shared" ref="E8:M8" si="3">L2</f>
         <v>0</v>
       </c>
       <c r="M8">
@@ -1961,12 +1961,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -2817,12 +2817,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -3673,12 +3673,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4529,12 +4529,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -5386,7 +5386,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E476BEC-D538-4958-8490-9E2E5CC869CE}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
     <col min="2" max="3" width="36.7109375" customWidth="1"/>
@@ -5397,7 +5397,7 @@
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -5405,22 +5405,22 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>41</v>
       </c>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="29.1">
       <c r="A9" s="8" t="s">
         <v>45</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="8" t="s">
         <v>47</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -5586,11 +5586,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="F14" t="s">
         <v>53</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="F15" t="s">
         <v>54</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>8.6666666666666663E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -5699,13 +5699,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -5965,17 +5965,11 @@
       <c r="AB2" s="5">
         <v>0</v>
       </c>
-      <c r="AC2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6060,17 +6054,11 @@
       <c r="AB3" s="5">
         <v>0</v>
       </c>
-      <c r="AC3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -6155,17 +6143,11 @@
       <c r="AB4" s="5">
         <v>0</v>
       </c>
-      <c r="AC4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -6250,17 +6232,11 @@
       <c r="AB5" s="5">
         <v>0</v>
       </c>
-      <c r="AC5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -6345,17 +6321,11 @@
       <c r="AB6" s="5">
         <v>0</v>
       </c>
-      <c r="AC6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -6440,17 +6410,11 @@
       <c r="AB7" s="5">
         <v>0</v>
       </c>
-      <c r="AC7" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -6465,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" ref="E8:AB8" si="1">E2</f>
+        <f t="shared" ref="E8:AE8" si="1">E2</f>
         <v>0</v>
       </c>
       <c r="F8" s="5">
@@ -6560,18 +6524,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC8" s="5">
-        <f t="shared" ref="AC8:AE8" si="2">AC2</f>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6585,12 +6540,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -6765,7 +6720,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -6854,17 +6809,8 @@
       <c r="AB2">
         <v>0</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6949,17 +6895,8 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -7044,17 +6981,8 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -7139,17 +7067,8 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -7234,17 +7153,8 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -7329,17 +7239,8 @@
       <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -7422,15 +7323,6 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -7445,12 +7337,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -7625,7 +7517,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -7710,17 +7602,8 @@
       <c r="AB2">
         <v>0</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -7805,17 +7688,8 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -7900,17 +7774,8 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -7995,17 +7860,8 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -8090,17 +7946,8 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -8185,17 +8032,8 @@
       <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -8278,15 +8116,6 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -8301,12 +8130,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -8481,7 +8310,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -8575,68 +8404,8 @@
       <c r="AE2">
         <v>0</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -8730,68 +8499,8 @@
       <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -8885,68 +8594,8 @@
       <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -9040,68 +8689,8 @@
       <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -9195,68 +8784,8 @@
       <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -9350,68 +8879,8 @@
       <c r="AE7">
         <v>0</v>
       </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -9503,66 +8972,6 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
         <v>0</v>
       </c>
     </row>
@@ -9577,12 +8986,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -9757,7 +9166,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -9855,68 +9264,8 @@
       <c r="AE2">
         <v>0</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -10010,68 +9359,8 @@
       <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -10165,68 +9454,8 @@
       <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -10320,68 +9549,8 @@
       <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -10479,68 +9648,8 @@
       <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -10634,68 +9743,8 @@
       <c r="AE7">
         <v>0</v>
       </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -10787,66 +9836,6 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
         <v>0</v>
       </c>
     </row>
@@ -10861,12 +9850,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -10961,7 +9950,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -11060,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -11155,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -11250,7 +10239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -11345,7 +10334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -11440,7 +10429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -11535,7 +10524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -11641,12 +10630,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -11821,7 +10810,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -11910,17 +10899,8 @@
       <c r="AB2">
         <v>0</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:51">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -12005,17 +10985,8 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:51">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -12100,17 +11071,8 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:51">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -12195,17 +11157,8 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:51">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -12295,17 +11248,8 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:51">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -12390,17 +11334,8 @@
       <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:51">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -12489,15 +11424,6 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -12508,6 +11434,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -12651,12 +11583,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -12667,36 +11593,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3285311B-1B6D-4F6C-81B6-71E492B53EFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3186AAB2-E363-4AC1-B7D2-1E1782AC568D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3186AAB2-E363-4AC1-B7D2-1E1782AC568D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EC9FC2-7EF6-445D-9670-080828A6194F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134A8D8-466C-43EA-A182-1DAFCE62A71F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134A8D8-466C-43EA-A182-1DAFCE62A71F}"/>
 </file>
--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27203"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/anuj_talwar_wri_org/Documents/EPS/Transport/Input Data/Draft US 4.0/BVS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{B81DBE57-2E0B-492A-8B39-306C57ECFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E09122C-4500-40D1-9C2B-7BAB581A9537}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ED3748-23E8-4E39-B218-7A33E409FEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="24165" windowHeight="13365" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,15 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId3"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId4"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId5"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId6"/>
-    <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId7"/>
-    <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId8"/>
+    <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId6"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId7"/>
+    <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId8"/>
     <sheet name="BVS-frgt-LDVs" sheetId="107" r:id="rId9"/>
     <sheet name="BVS-frgt-HDVs" sheetId="108" r:id="rId10"/>
     <sheet name="BVS-frgt-aircraft" sheetId="109" r:id="rId11"/>
-    <sheet name="BVS-frgt-rail" sheetId="110" r:id="rId12"/>
-    <sheet name="BVS-frgt-ships" sheetId="111" r:id="rId13"/>
-    <sheet name="BVS-frgt-motorbikes" sheetId="112" r:id="rId14"/>
+    <sheet name="BVS-frgt-motorbikes" sheetId="112" r:id="rId12"/>
+    <sheet name="BVS-frgt-rail" sheetId="110" r:id="rId13"/>
+    <sheet name="BVS-frgt-ships" sheetId="111" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -260,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,7 +473,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -511,6 +511,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="33">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -541,7 +542,7 @@
     <cellStyle name="Parent row 2" xfId="28" xr:uid="{1C336998-EB49-46ED-B880-BDD7385C1A9F}"/>
     <cellStyle name="Parent row 3" xfId="21" xr:uid="{E39AA093-46A1-425E-9FAB-5E5D22915C9B}"/>
     <cellStyle name="Parent row 4" xfId="13" xr:uid="{766EEC84-3128-426E-8720-CF77BEFFA340}"/>
-    <cellStyle name="Per cent" xfId="30" builtinId="5"/>
+    <cellStyle name="Percent" xfId="30" builtinId="5"/>
     <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Table title 2" xfId="29" xr:uid="{75C5CFB8-5852-4F3E-A011-ECC9372E7F45}"/>
     <cellStyle name="Table title 3" xfId="22" xr:uid="{D3D003D1-845D-4DC8-878D-F5771072DB44}"/>
@@ -847,18 +848,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -874,7 +876,7 @@
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,7 +884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -890,7 +892,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -898,7 +900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -906,7 +908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -914,119 +916,119 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>54.77</v>
       </c>
@@ -1037,7 +1039,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>75.807100000000005</v>
       </c>
@@ -1045,22 +1047,22 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>10000000</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>100000</v>
       </c>
@@ -1078,16 +1080,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF139E4-90E8-4DFC-ABC4-1799BB0C313F}">
-  <sheetPr>
+  <sheetPr codeName="Sheet10">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -1262,7 +1264,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1368,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -1463,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1558,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1653,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1758,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -1853,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1888,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="E8:M8" si="3">L2</f>
+        <f t="shared" ref="L8:M8" si="3">L2</f>
         <v>0</v>
       </c>
       <c r="M8">
@@ -1957,16 +1959,16 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1274E315-3F6B-4E92-87B5-9C3C1B4F85DA}">
-  <sheetPr>
+  <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -2141,7 +2143,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -2236,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2331,7 +2333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -2426,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2521,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2616,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -2711,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -2812,17 +2814,17 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51E62EB-7B15-406D-A4C2-A4FF0C772B4A}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F53C0-8CAC-4671-B512-864662BE4DD4}">
+  <sheetPr codeName="Sheet14">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -2997,21 +2999,25 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <f>'FAME II'!C9</f>
+        <v>912.90852656563811</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <f>B2</f>
+        <v>912.90852656563811</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <f t="shared" ref="D2:E2" si="1">C2</f>
+        <v>912.90852656563811</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>912.90852656563811</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3092,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -3187,7 +3193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -3282,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -3377,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -3472,7 +3478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -3567,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -3668,17 +3674,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44835A4-EB4E-4E1F-85F1-DB244E55CC6B}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51E62EB-7B15-406D-A4C2-A4FF0C772B4A}">
+  <sheetPr codeName="Sheet12">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -3853,7 +3859,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -4043,7 +4049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -4233,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -4328,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -4423,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4524,17 +4530,17 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F53C0-8CAC-4671-B512-864662BE4DD4}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44835A4-EB4E-4E1F-85F1-DB244E55CC6B}">
+  <sheetPr codeName="Sheet13">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -4709,25 +4715,21 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
       <c r="B2">
-        <f>'FAME II'!C9</f>
-        <v>912.90852656563811</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <f>B2</f>
-        <v>912.90852656563811</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:E2" si="1">C2</f>
-        <v>912.90852656563811</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f t="shared" si="1"/>
-        <v>912.90852656563811</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4808,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -4903,7 +4905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -4998,7 +5000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -5093,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -5188,7 +5190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -5283,7 +5285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -5385,8 +5387,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E476BEC-D538-4958-8490-9E2E5CC869CE}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
     <col min="2" max="3" width="36.7109375" customWidth="1"/>
@@ -5397,7 +5400,7 @@
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -5405,22 +5408,22 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -5440,7 +5443,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>41</v>
       </c>
@@ -5455,21 +5458,21 @@
       </c>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>43</v>
       </c>
       <c r="B8">
         <v>20000</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="19">
         <f>B8/About!A$33</f>
         <v>365.16341062625526</v>
       </c>
       <c r="D8" s="5">
         <v>30000</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="19">
         <f>D8/About!A$33</f>
         <v>547.7451159393828</v>
       </c>
@@ -5481,7 +5484,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="29.1">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>45</v>
       </c>
@@ -5507,7 +5510,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>47</v>
       </c>
@@ -5533,7 +5536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -5560,7 +5563,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -5586,11 +5589,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>53</v>
       </c>
@@ -5598,7 +5601,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
         <v>54</v>
       </c>
@@ -5606,7 +5609,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -5618,7 +5621,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5632,7 +5635,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -5646,7 +5649,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -5660,7 +5663,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -5674,7 +5677,7 @@
         <v>8.6666666666666663E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -5695,17 +5698,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -5880,7 +5883,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -5969,7 +5972,7 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6058,7 +6061,7 @@
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -6147,7 +6150,7 @@
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -6236,7 +6239,7 @@
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -6325,7 +6328,7 @@
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -6414,7 +6417,7 @@
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -6429,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" ref="E8:AE8" si="1">E2</f>
+        <f t="shared" ref="E8:AB8" si="1">E2</f>
         <v>0</v>
       </c>
       <c r="F8" s="5">
@@ -6536,16 +6539,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55534DDE-5D7D-440E-9F2D-C8BE7EE78DD9}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -6720,7 +6723,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -6810,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6896,7 +6899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -6982,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -7068,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -7154,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -7240,7 +7243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -7333,16 +7336,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1741F6-596C-4C6D-91F8-CA5AA118CF11}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -7517,7 +7520,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -7603,7 +7606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -7689,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -7775,7 +7778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -7861,7 +7864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -7947,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -8033,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -8125,17 +8128,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A94405-868B-4452-B9AC-D6B63E4037BA}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C5C6BF-BE7A-4625-8CB5-34C673B46C4E}">
+  <sheetPr codeName="Sheet8">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -8229,749 +8232,673 @@
       <c r="AE1">
         <v>2050</v>
       </c>
-      <c r="AF1">
-        <f>AE1+1</f>
-        <v>2051</v>
-      </c>
-      <c r="AG1">
-        <f t="shared" ref="AG1:AY1" si="0">AF1+1</f>
-        <v>2052</v>
-      </c>
-      <c r="AH1">
-        <f t="shared" si="0"/>
-        <v>2053</v>
-      </c>
-      <c r="AI1">
-        <f t="shared" si="0"/>
-        <v>2054</v>
-      </c>
-      <c r="AJ1">
-        <f t="shared" si="0"/>
-        <v>2055</v>
-      </c>
-      <c r="AK1">
-        <f t="shared" si="0"/>
-        <v>2056</v>
-      </c>
-      <c r="AL1">
-        <f t="shared" si="0"/>
-        <v>2057</v>
-      </c>
-      <c r="AM1">
-        <f t="shared" si="0"/>
-        <v>2058</v>
-      </c>
-      <c r="AN1">
-        <f t="shared" si="0"/>
-        <v>2059</v>
-      </c>
-      <c r="AO1">
-        <f t="shared" si="0"/>
-        <v>2060</v>
-      </c>
-      <c r="AP1">
-        <f t="shared" si="0"/>
-        <v>2061</v>
-      </c>
-      <c r="AQ1">
-        <f t="shared" si="0"/>
-        <v>2062</v>
-      </c>
-      <c r="AR1">
-        <f t="shared" si="0"/>
-        <v>2063</v>
-      </c>
-      <c r="AS1">
-        <f t="shared" si="0"/>
-        <v>2064</v>
-      </c>
-      <c r="AT1">
-        <f t="shared" si="0"/>
-        <v>2065</v>
-      </c>
-      <c r="AU1">
-        <f t="shared" si="0"/>
-        <v>2066</v>
-      </c>
-      <c r="AV1">
-        <f t="shared" si="0"/>
-        <v>2067</v>
-      </c>
-      <c r="AW1">
-        <f>AV1+1</f>
-        <v>2068</v>
-      </c>
-      <c r="AX1">
-        <f t="shared" si="0"/>
-        <v>2069</v>
-      </c>
-      <c r="AY1">
-        <f t="shared" si="0"/>
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51">
+      <c r="B2" s="19">
+        <f>'FAME II'!C8</f>
+        <v>365.16341062625526</v>
+      </c>
+      <c r="C2" s="19">
+        <f>'FAME II'!E8</f>
+        <v>547.7451159393828</v>
+      </c>
+      <c r="D2" s="19">
+        <f>C2</f>
+        <v>547.7451159393828</v>
+      </c>
+      <c r="E2" s="19">
+        <f>D2</f>
+        <v>547.7451159393828</v>
+      </c>
+      <c r="F2" s="19">
+        <v>0</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0</v>
+      </c>
+      <c r="H2" s="19">
+        <v>0</v>
+      </c>
+      <c r="I2" s="19">
+        <v>0</v>
+      </c>
+      <c r="J2" s="19">
+        <v>0</v>
+      </c>
+      <c r="K2" s="19">
+        <v>0</v>
+      </c>
+      <c r="L2" s="19">
+        <v>0</v>
+      </c>
+      <c r="M2" s="19">
+        <v>0</v>
+      </c>
+      <c r="N2" s="19">
+        <v>0</v>
+      </c>
+      <c r="O2" s="19">
+        <v>0</v>
+      </c>
+      <c r="P2" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="19">
+        <v>0</v>
+      </c>
+      <c r="R2" s="19">
+        <v>0</v>
+      </c>
+      <c r="S2" s="19">
+        <v>0</v>
+      </c>
+      <c r="T2" s="19">
+        <v>0</v>
+      </c>
+      <c r="U2" s="19">
+        <v>0</v>
+      </c>
+      <c r="V2" s="19">
+        <v>0</v>
+      </c>
+      <c r="W2" s="19">
+        <v>0</v>
+      </c>
+      <c r="X2" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51">
+      <c r="B3" s="19">
+        <v>0</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0</v>
+      </c>
+      <c r="F3" s="19">
+        <v>0</v>
+      </c>
+      <c r="G3" s="19">
+        <v>0</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0</v>
+      </c>
+      <c r="I3" s="19">
+        <v>0</v>
+      </c>
+      <c r="J3" s="19">
+        <v>0</v>
+      </c>
+      <c r="K3" s="19">
+        <v>0</v>
+      </c>
+      <c r="L3" s="19">
+        <v>0</v>
+      </c>
+      <c r="M3" s="19">
+        <v>0</v>
+      </c>
+      <c r="N3" s="19">
+        <v>0</v>
+      </c>
+      <c r="O3" s="19">
+        <v>0</v>
+      </c>
+      <c r="P3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>0</v>
+      </c>
+      <c r="R3" s="19">
+        <v>0</v>
+      </c>
+      <c r="S3" s="19">
+        <v>0</v>
+      </c>
+      <c r="T3" s="19">
+        <v>0</v>
+      </c>
+      <c r="U3" s="19">
+        <v>0</v>
+      </c>
+      <c r="V3" s="19">
+        <v>0</v>
+      </c>
+      <c r="W3" s="19">
+        <v>0</v>
+      </c>
+      <c r="X3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51">
+      <c r="B4" s="19">
+        <v>0</v>
+      </c>
+      <c r="C4" s="19">
+        <v>0</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0</v>
+      </c>
+      <c r="F4" s="19">
+        <v>0</v>
+      </c>
+      <c r="G4" s="19">
+        <v>0</v>
+      </c>
+      <c r="H4" s="19">
+        <v>0</v>
+      </c>
+      <c r="I4" s="19">
+        <v>0</v>
+      </c>
+      <c r="J4" s="19">
+        <v>0</v>
+      </c>
+      <c r="K4" s="19">
+        <v>0</v>
+      </c>
+      <c r="L4" s="19">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
+        <v>0</v>
+      </c>
+      <c r="O4" s="19">
+        <v>0</v>
+      </c>
+      <c r="P4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>0</v>
+      </c>
+      <c r="R4" s="19">
+        <v>0</v>
+      </c>
+      <c r="S4" s="19">
+        <v>0</v>
+      </c>
+      <c r="T4" s="19">
+        <v>0</v>
+      </c>
+      <c r="U4" s="19">
+        <v>0</v>
+      </c>
+      <c r="V4" s="19">
+        <v>0</v>
+      </c>
+      <c r="W4" s="19">
+        <v>0</v>
+      </c>
+      <c r="X4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51">
+      <c r="B5" s="19">
+        <v>0</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="19">
+        <v>0</v>
+      </c>
+      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
+        <v>0</v>
+      </c>
+      <c r="O5" s="19">
+        <v>0</v>
+      </c>
+      <c r="P5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>0</v>
+      </c>
+      <c r="R5" s="19">
+        <v>0</v>
+      </c>
+      <c r="S5" s="19">
+        <v>0</v>
+      </c>
+      <c r="T5" s="19">
+        <v>0</v>
+      </c>
+      <c r="U5" s="19">
+        <v>0</v>
+      </c>
+      <c r="V5" s="19">
+        <v>0</v>
+      </c>
+      <c r="W5" s="19">
+        <v>0</v>
+      </c>
+      <c r="X5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51">
+      <c r="B6" s="19">
+        <v>0</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>0</v>
+      </c>
+      <c r="R6" s="19">
+        <v>0</v>
+      </c>
+      <c r="S6" s="19">
+        <v>0</v>
+      </c>
+      <c r="T6" s="19">
+        <v>0</v>
+      </c>
+      <c r="U6" s="19">
+        <v>0</v>
+      </c>
+      <c r="V6" s="19">
+        <v>0</v>
+      </c>
+      <c r="W6" s="19">
+        <v>0</v>
+      </c>
+      <c r="X6" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51">
+      <c r="B7" s="19">
+        <v>0</v>
+      </c>
+      <c r="C7" s="19">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19">
+        <v>0</v>
+      </c>
+      <c r="F7" s="19">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0</v>
+      </c>
+      <c r="L7" s="19">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19">
+        <v>0</v>
+      </c>
+      <c r="N7" s="19">
+        <v>0</v>
+      </c>
+      <c r="O7" s="19">
+        <v>0</v>
+      </c>
+      <c r="P7" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>0</v>
+      </c>
+      <c r="R7" s="19">
+        <v>0</v>
+      </c>
+      <c r="S7" s="19">
+        <v>0</v>
+      </c>
+      <c r="T7" s="19">
+        <v>0</v>
+      </c>
+      <c r="U7" s="19">
+        <v>0</v>
+      </c>
+      <c r="V7" s="19">
+        <v>0</v>
+      </c>
+      <c r="W7" s="19">
+        <v>0</v>
+      </c>
+      <c r="X7" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
+      <c r="B8" s="19">
+        <v>0</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0</v>
+      </c>
+      <c r="P8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>0</v>
+      </c>
+      <c r="R8" s="19">
+        <v>0</v>
+      </c>
+      <c r="S8" s="19">
+        <v>0</v>
+      </c>
+      <c r="T8" s="19">
+        <v>0</v>
+      </c>
+      <c r="U8" s="19">
+        <v>0</v>
+      </c>
+      <c r="V8" s="19">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19">
+        <v>0</v>
+      </c>
+      <c r="X8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="19">
         <v>0</v>
       </c>
     </row>
@@ -8981,17 +8908,794 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A94405-868B-4452-B9AC-D6B63E4037BA}">
+  <sheetPr codeName="Sheet6">
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E87FBF-8038-4912-A5A6-BE7241A5CAB0}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -9166,7 +9870,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -9265,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -9360,7 +10064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -9455,7 +10159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -9550,7 +10254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -9649,7 +10353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -9744,787 +10448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C5C6BF-BE7A-4625-8CB5-34C673B46C4E}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1">
-        <v>2021</v>
-      </c>
-      <c r="C1">
-        <v>2022</v>
-      </c>
-      <c r="D1">
-        <v>2023</v>
-      </c>
-      <c r="E1">
-        <v>2024</v>
-      </c>
-      <c r="F1">
-        <v>2025</v>
-      </c>
-      <c r="G1">
-        <v>2026</v>
-      </c>
-      <c r="H1">
-        <v>2027</v>
-      </c>
-      <c r="I1">
-        <v>2028</v>
-      </c>
-      <c r="J1">
-        <v>2029</v>
-      </c>
-      <c r="K1">
-        <v>2030</v>
-      </c>
-      <c r="L1">
-        <v>2031</v>
-      </c>
-      <c r="M1">
-        <v>2032</v>
-      </c>
-      <c r="N1">
-        <v>2033</v>
-      </c>
-      <c r="O1">
-        <v>2034</v>
-      </c>
-      <c r="P1">
-        <v>2035</v>
-      </c>
-      <c r="Q1">
-        <v>2036</v>
-      </c>
-      <c r="R1">
-        <v>2037</v>
-      </c>
-      <c r="S1">
-        <v>2038</v>
-      </c>
-      <c r="T1">
-        <v>2039</v>
-      </c>
-      <c r="U1">
-        <v>2040</v>
-      </c>
-      <c r="V1">
-        <v>2041</v>
-      </c>
-      <c r="W1">
-        <v>2042</v>
-      </c>
-      <c r="X1">
-        <v>2043</v>
-      </c>
-      <c r="Y1">
-        <v>2044</v>
-      </c>
-      <c r="Z1">
-        <v>2045</v>
-      </c>
-      <c r="AA1">
-        <v>2046</v>
-      </c>
-      <c r="AB1">
-        <v>2047</v>
-      </c>
-      <c r="AC1">
-        <v>2048</v>
-      </c>
-      <c r="AD1">
-        <v>2049</v>
-      </c>
-      <c r="AE1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2">
-        <f>'FAME II'!C8</f>
-        <v>365.16341062625526</v>
-      </c>
-      <c r="C2" s="5">
-        <f>'FAME II'!E8</f>
-        <v>547.7451159393828</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2</f>
-        <v>547.7451159393828</v>
-      </c>
-      <c r="E2" s="5">
-        <f>D2</f>
-        <v>547.7451159393828</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -10626,16 +10550,16 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB978D3-75FC-40E7-B55E-E0DE8CD249DB}">
-  <sheetPr>
+  <sheetPr codeName="Sheet9">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -10810,7 +10734,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -10900,7 +10824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -10986,7 +10910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -11072,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -11158,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -11249,7 +11173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -11335,7 +11259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -11434,9 +11358,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11584,22 +11511,42 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3186AAB2-E363-4AC1-B7D2-1E1782AC568D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134A8D8-466C-43EA-A182-1DAFCE62A71F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EC9FC2-7EF6-445D-9670-080828A6194F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EC9FC2-7EF6-445D-9670-080828A6194F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134A8D8-466C-43EA-A182-1DAFCE62A71F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3186AAB2-E363-4AC1-B7D2-1E1782AC568D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>